--- a/Exemplo_encode.xlsx
+++ b/Exemplo_encode.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vera/Documents/GitHub/SEED/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58DF1E60-2523-4841-8E02-6E3FE6DAF27D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A9ED7AA-85C2-5345-B88C-B42BA270DDEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5280" yWindow="7920" windowWidth="22160" windowHeight="8360" xr2:uid="{BC1145FC-44B2-8E4A-B352-2463BCCE776C}"/>
+    <workbookView xWindow="5520" yWindow="7280" windowWidth="22160" windowHeight="8360" xr2:uid="{BC1145FC-44B2-8E4A-B352-2463BCCE776C}"/>
   </bookViews>
   <sheets>
     <sheet name="Folha1" sheetId="1" r:id="rId1"/>
@@ -36,22 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
-  <si>
-    <t>scene_encode</t>
-  </si>
-  <si>
-    <t>scene_size</t>
-  </si>
-  <si>
-    <t>object_encode</t>
-  </si>
-  <si>
-    <t>object_size</t>
-  </si>
-  <si>
-    <t>condition_encode</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="33">
   <si>
     <t>Index</t>
   </si>
@@ -62,63 +47,15 @@
     <t>incongruent</t>
   </si>
   <si>
-    <t>Scenes_Dataset/museum_A.jpg</t>
-  </si>
-  <si>
-    <t>lure</t>
-  </si>
-  <si>
-    <t>Objects_Dataset/fluorescent_bracelets.jpg</t>
-  </si>
-  <si>
-    <t>Objects_Dataset/picnic_towel.jpg</t>
-  </si>
-  <si>
-    <t>Objects_Dataset/3d_glasses.jpg</t>
-  </si>
-  <si>
-    <t>Objects_Dataset/movie_reels.jpg</t>
-  </si>
-  <si>
-    <t>Scenes_Dataset/movie_theater_A.jpg</t>
-  </si>
-  <si>
-    <t>lure_size</t>
-  </si>
-  <si>
     <t>(300,300)</t>
   </si>
   <si>
     <t>(350,268)</t>
   </si>
   <si>
-    <t>(600,364)</t>
-  </si>
-  <si>
-    <t>(600,337)</t>
-  </si>
-  <si>
-    <t>Scenes_Dataset/building_entrance_A.jpg</t>
-  </si>
-  <si>
     <t>ex_new</t>
   </si>
   <si>
-    <t>Scenes_Dataset/boat_interior_A.jpg</t>
-  </si>
-  <si>
-    <t>(600,400)</t>
-  </si>
-  <si>
-    <t>new_scene_size</t>
-  </si>
-  <si>
-    <t>lure_pos</t>
-  </si>
-  <si>
-    <t>target_pos</t>
-  </si>
-  <si>
     <t>jitter_ITI</t>
   </si>
   <si>
@@ -129,6 +66,75 @@
   </si>
   <si>
     <t>(300, -200)</t>
+  </si>
+  <si>
+    <t>Objects_Dataset/3d_glasses_retouched.png</t>
+  </si>
+  <si>
+    <t>Objects_Dataset/abacus.png</t>
+  </si>
+  <si>
+    <t>Objects_Dataset/airplane_belt.png</t>
+  </si>
+  <si>
+    <t>Objects_Dataset/basketball.png</t>
+  </si>
+  <si>
+    <t>ex_scene_encode</t>
+  </si>
+  <si>
+    <t>ex_scene_size</t>
+  </si>
+  <si>
+    <t>ex_object_encode</t>
+  </si>
+  <si>
+    <t>ex_object_size</t>
+  </si>
+  <si>
+    <t>ex_target_pos</t>
+  </si>
+  <si>
+    <t>ex_condition_encode</t>
+  </si>
+  <si>
+    <t>ex_lure_size</t>
+  </si>
+  <si>
+    <t>ex_lure_pos</t>
+  </si>
+  <si>
+    <t>ex_new_scene_size</t>
+  </si>
+  <si>
+    <t>ex_lure</t>
+  </si>
+  <si>
+    <t>Scenes_Dataset/painting_workshop_A.jpg</t>
+  </si>
+  <si>
+    <t>Scenes_Dataset/sky_A.jpg</t>
+  </si>
+  <si>
+    <t>(600,398)</t>
+  </si>
+  <si>
+    <t>(600,450)</t>
+  </si>
+  <si>
+    <t>Ex1</t>
+  </si>
+  <si>
+    <t>Ex2</t>
+  </si>
+  <si>
+    <t>Scenes_Dataset/temple_A.jpg</t>
+  </si>
+  <si>
+    <t>(600,358)</t>
+  </si>
+  <si>
+    <t>Scenes_Dataset/athletics_track_A</t>
   </si>
 </sst>
 </file>
@@ -545,125 +551,125 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="L1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2">
+      <c r="A2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="4" t="s">
+      <c r="H2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" t="s">
         <v>30</v>
       </c>
-      <c r="G2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="K2" t="s">
-        <v>20</v>
-      </c>
       <c r="L2" s="5" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="M2">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3">
+      <c r="A3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="H3" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="I3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3" t="s">
         <v>7</v>
-      </c>
-      <c r="H3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="K3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/Exemplo_encode.xlsx
+++ b/Exemplo_encode.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vera/Documents/GitHub/SEED/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A9ED7AA-85C2-5345-B88C-B42BA270DDEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FD706F4-8F12-EB4E-9BD6-FC831B28A65D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5520" yWindow="7280" windowWidth="22160" windowHeight="8360" xr2:uid="{BC1145FC-44B2-8E4A-B352-2463BCCE776C}"/>
+    <workbookView xWindow="2240" yWindow="3600" windowWidth="23480" windowHeight="10980" xr2:uid="{BC1145FC-44B2-8E4A-B352-2463BCCE776C}"/>
   </bookViews>
   <sheets>
     <sheet name="Folha1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="40">
   <si>
     <t>Index</t>
   </si>
@@ -50,9 +50,6 @@
     <t>(300,300)</t>
   </si>
   <si>
-    <t>(350,268)</t>
-  </si>
-  <si>
     <t>ex_new</t>
   </si>
   <si>
@@ -68,18 +65,6 @@
     <t>(300, -200)</t>
   </si>
   <si>
-    <t>Objects_Dataset/3d_glasses_retouched.png</t>
-  </si>
-  <si>
-    <t>Objects_Dataset/abacus.png</t>
-  </si>
-  <si>
-    <t>Objects_Dataset/airplane_belt.png</t>
-  </si>
-  <si>
-    <t>Objects_Dataset/basketball.png</t>
-  </si>
-  <si>
     <t>ex_scene_encode</t>
   </si>
   <si>
@@ -135,6 +120,42 @@
   </si>
   <si>
     <t>Scenes_Dataset/athletics_track_A</t>
+  </si>
+  <si>
+    <t>Objects_Dataset/hang_glider.png</t>
+  </si>
+  <si>
+    <t>(450,275)</t>
+  </si>
+  <si>
+    <t>Objects_Dataset/fish_hook.png</t>
+  </si>
+  <si>
+    <t>(130,200)</t>
+  </si>
+  <si>
+    <t>Objects_Dataset/drone.png</t>
+  </si>
+  <si>
+    <t>(300,144)</t>
+  </si>
+  <si>
+    <t>Objects_Dataset/barrier.png</t>
+  </si>
+  <si>
+    <t>Ex3</t>
+  </si>
+  <si>
+    <t>Ex4</t>
+  </si>
+  <si>
+    <t>Scenes_Dataset/cellars_A.jpg</t>
+  </si>
+  <si>
+    <t>(600,399)</t>
+  </si>
+  <si>
+    <t>Scenes_Dataset/river_B.jpg</t>
   </si>
 </sst>
 </file>
@@ -537,7 +558,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92C3CBF2-7D11-D543-997C-E7879DA53727}">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="29.6640625" customWidth="1"/>
@@ -554,78 +575,78 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C1" t="s">
+      <c r="H1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="K1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="3" t="s">
         <v>5</v>
-      </c>
-      <c r="L1" t="s">
-        <v>22</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
         <v>28</v>
       </c>
-      <c r="B2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
       <c r="E2" s="4" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G2" t="s">
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="M2">
         <v>2</v>
@@ -633,43 +654,113 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G3" t="s">
         <v>2</v>
       </c>
       <c r="H3" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>3</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" t="s">
+        <v>2</v>
+      </c>
+      <c r="H4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
         <v>32</v>
       </c>
-      <c r="L3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M3" t="s">
+      <c r="E5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>7</v>
+      </c>
+      <c r="G5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="M5" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/Exemplo_encode.xlsx
+++ b/Exemplo_encode.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vera/Documents/GitHub/SEED/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FD706F4-8F12-EB4E-9BD6-FC831B28A65D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F27B8E1-07D6-1144-9FD0-14D43A6734EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2240" yWindow="3600" windowWidth="23480" windowHeight="10980" xr2:uid="{BC1145FC-44B2-8E4A-B352-2463BCCE776C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="35">
   <si>
     <t>Index</t>
   </si>
@@ -50,9 +50,6 @@
     <t>(300,300)</t>
   </si>
   <si>
-    <t>ex_new</t>
-  </si>
-  <si>
     <t>jitter_ITI</t>
   </si>
   <si>
@@ -89,9 +86,6 @@
     <t>ex_lure_pos</t>
   </si>
   <si>
-    <t>ex_new_scene_size</t>
-  </si>
-  <si>
     <t>ex_lure</t>
   </si>
   <si>
@@ -111,15 +105,6 @@
   </si>
   <si>
     <t>Ex2</t>
-  </si>
-  <si>
-    <t>Scenes_Dataset/temple_A.jpg</t>
-  </si>
-  <si>
-    <t>(600,358)</t>
-  </si>
-  <si>
-    <t>Scenes_Dataset/athletics_track_A</t>
   </si>
   <si>
     <t>Objects_Dataset/hang_glider.png</t>
@@ -558,7 +543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92C3CBF2-7D11-D543-997C-E7879DA53727}">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="29.6640625" customWidth="1"/>
@@ -566,201 +551,181 @@
     <col min="5" max="6" width="14.5" customWidth="1"/>
     <col min="7" max="7" width="15.1640625" customWidth="1"/>
     <col min="8" max="8" width="43" customWidth="1"/>
-    <col min="11" max="11" width="34.83203125" customWidth="1"/>
-    <col min="12" max="12" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
         <v>9</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="J1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
         <v>18</v>
       </c>
-      <c r="I1" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="L1" t="s">
-        <v>17</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="C2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
         <v>23</v>
       </c>
-      <c r="B2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" t="s">
-        <v>28</v>
-      </c>
       <c r="E2" s="4" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G2" t="s">
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
         <v>25</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>31</v>
-      </c>
       <c r="F3" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G3" t="s">
         <v>2</v>
       </c>
       <c r="H3" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>3</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K3" t="s">
-        <v>27</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="M3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>3</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G4" t="s">
         <v>2</v>
       </c>
       <c r="H4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="I4" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="M4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>33</v>
-      </c>
       <c r="F5" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G5" t="s">
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="M5" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="K5" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Exemplo_encode.xlsx
+++ b/Exemplo_encode.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vera/Documents/GitHub/SEED/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FD706F4-8F12-EB4E-9BD6-FC831B28A65D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42CBDF76-3231-B74F-AB07-9486D743FD66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2240" yWindow="3600" windowWidth="23480" windowHeight="10980" xr2:uid="{BC1145FC-44B2-8E4A-B352-2463BCCE776C}"/>
   </bookViews>
@@ -561,7 +561,7 @@
   <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="29.6640625" customWidth="1"/>
+    <col min="2" max="2" width="35.6640625" customWidth="1"/>
     <col min="4" max="4" width="30.33203125" customWidth="1"/>
     <col min="5" max="6" width="14.5" customWidth="1"/>
     <col min="7" max="7" width="15.1640625" customWidth="1"/>
